--- a/VerveStacks_DNK_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DNK_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DNK_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5135B94A-EB6B-4051-9E4F-3E627AC08875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE56720-97C8-4356-AFBF-F9C672F4BC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="429">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1412,6 +1412,9 @@
   </si>
   <si>
     <t>Transformer: e_w98526640-220 → e_w98526640-400</t>
+  </si>
+  <si>
+    <t>e_DK1-400,e_DK16-400,e_DK19-400,e_DK2-400,e_DK21-400,e_DK22-220,e_DK26-400,e_DK27-400,e_DK3-400,e_DK4-400,e_DK5-400,e_DK6-220,e_w131339683-400,e_w133555503-400,e_w1384028957,e_w1384028957-400,e_w199713891-400,e_w250212215-400,e_w26931725-220,e_w26931725-400,e_w301369285-400,e_w42128776-400,e_w93624851-400,e_w94092312-400,e_w98212652-400,e_w98216482,e_w98216482-400</t>
   </si>
 </sst>
 </file>
@@ -3305,7 +3308,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_DK1-400,e_DK16-400,e_DK19-400,e_DK2-400,e_DK21-400,e_DK22-220,e_DK26-400,e_DK27-400,e_DK3-400,e_DK4-400,e_DK5-400,e_DK6-220,e_w131339683-400,e_w133555503-400,e_w1384028957,e_w1384028957-400,e_w199713891-400,e_w250212215-400,e_w26931725-220,e_w26931725-400,e_w301369285-400,e_w42128776-400,e_w93624851-400,e_w94092312-400,e_w98212652-400,e_w98216482,e_w98216482-400</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3327,7 +3330,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_DK1-400,e_DK16-400,e_DK19-400,e_DK2-400,e_DK21-400,e_DK22-220,e_DK26-400,e_DK27-400,e_DK3-400,e_DK4-400,e_DK5-400,e_DK6-220,e_w131339683-400,e_w133555503-400,e_w1384028957,e_w1384028957-400,e_w199713891-400,e_w250212215-400,e_w26931725-220,e_w26931725-400,e_w301369285-400,e_w42128776-400,e_w93624851-400,e_w94092312-400,e_w98212652-400,e_w98216482,e_w98216482-400</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3342,7 +3345,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
